--- a/artfynd/A 9057-2023 artfynd.xlsx
+++ b/artfynd/A 9057-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9057-2023 artfynd.xlsx
+++ b/artfynd/A 9057-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67530747</v>
+        <v>67530781</v>
       </c>
       <c r="B2" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1841</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540146.0247104575</v>
+        <v>540136</v>
       </c>
       <c r="R2" t="n">
-        <v>7232435.418785081</v>
+        <v>7232370</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2017-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -780,44 +780,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson</t>
+          <t>Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68654375</v>
+        <v>68654333</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541032.1794666076</v>
+        <v>540917</v>
       </c>
       <c r="R3" t="n">
-        <v>7232997.06448391</v>
+        <v>7232831</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68654380</v>
+        <v>68654340</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540759.9934689801</v>
+        <v>540439</v>
       </c>
       <c r="R4" t="n">
-        <v>7233080.173123333</v>
+        <v>7232783</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68654374</v>
+        <v>68654344</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541037.9096308898</v>
+        <v>540439</v>
       </c>
       <c r="R5" t="n">
-        <v>7233008.05679776</v>
+        <v>7232846</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68654354</v>
+        <v>68654386</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540555.9699357441</v>
+        <v>540249</v>
       </c>
       <c r="R6" t="n">
-        <v>7233066.030395426</v>
+        <v>7233109</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,55 +1215,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68654345</v>
+        <v>68654376</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>918</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540589.9249578373</v>
+        <v>541024</v>
       </c>
       <c r="R7" t="n">
-        <v>7232919.176692314</v>
+        <v>7232968</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1320,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,37 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68654394</v>
+        <v>68654391</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540169.0161448445</v>
+        <v>540330</v>
       </c>
       <c r="R8" t="n">
-        <v>7233093.055495967</v>
+        <v>7233059</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,15 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68654386</v>
+        <v>67530612</v>
       </c>
       <c r="B9" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,37 +1440,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krutskogen, Ås lm</t>
+          <t>Antonskullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540249.058684895</v>
+        <v>540139</v>
       </c>
       <c r="R9" t="n">
-        <v>7233108.835503909</v>
+        <v>7232440</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,22 +1494,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,49 +1514,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström, Nils Ericson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68654372</v>
+        <v>68654383</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540990.1331375547</v>
+        <v>540280</v>
       </c>
       <c r="R10" t="n">
-        <v>7233119.874672063</v>
+        <v>7233154</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1656,7 +1596,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,15 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68654392</v>
+        <v>68654402</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,39 +1644,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540410.8491260356</v>
+        <v>540264</v>
       </c>
       <c r="R11" t="n">
-        <v>7233077.050610125</v>
+        <v>7232876</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1773,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,15 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68654390</v>
+        <v>68654334</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540300.8802808158</v>
+        <v>540911</v>
       </c>
       <c r="R12" t="n">
-        <v>7233067.992232204</v>
+        <v>7232830</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1885,7 +1810,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1820,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,15 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68654389</v>
+        <v>68654341</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,39 +1858,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540268.1736454682</v>
+        <v>540438</v>
       </c>
       <c r="R13" t="n">
-        <v>7233062.929043113</v>
+        <v>7232788</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2002,7 +1917,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +1927,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,15 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68654384</v>
+        <v>68654364</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540286.9476334309</v>
+        <v>540903</v>
       </c>
       <c r="R14" t="n">
-        <v>7233165.171872125</v>
+        <v>7233213</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2114,7 +2024,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2034,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,37 +2061,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>68654376</v>
+        <v>68654377</v>
       </c>
       <c r="B15" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>918</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2191,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541024.1792618396</v>
+        <v>540816</v>
       </c>
       <c r="R15" t="n">
-        <v>7232967.992599824</v>
+        <v>7233009</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2226,7 +2131,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2141,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,15 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68654363</v>
+        <v>68654384</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540941.2025453671</v>
+        <v>540287</v>
       </c>
       <c r="R16" t="n">
-        <v>7232981.950355588</v>
+        <v>7233165</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2338,7 +2238,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2248,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,53 +2275,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>68654343</v>
+        <v>67530598</v>
       </c>
       <c r="B17" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Krutskogen, Ås lm</t>
+          <t>Antonskullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540427.0974062243</v>
+        <v>540139</v>
       </c>
       <c r="R17" t="n">
-        <v>7232841.809915761</v>
+        <v>7232357</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,22 +2340,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,49 +2360,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström, Nils Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68654383</v>
+        <v>68654403</v>
       </c>
       <c r="B18" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2527,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540279.9546793194</v>
+        <v>540281</v>
       </c>
       <c r="R18" t="n">
-        <v>7233154.164439422</v>
+        <v>7232884</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2562,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2452,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,37 +2479,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>68654350</v>
+        <v>68654408</v>
       </c>
       <c r="B19" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540631.176837276</v>
+        <v>540336</v>
       </c>
       <c r="R19" t="n">
-        <v>7232975.14774335</v>
+        <v>7232733</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2674,7 +2549,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2559,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,15 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>68654347</v>
+        <v>68654339</v>
       </c>
       <c r="B20" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2751,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540585.1821878895</v>
+        <v>540734</v>
       </c>
       <c r="R20" t="n">
-        <v>7232927.925724796</v>
+        <v>7232848</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2786,7 +2656,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2666,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,15 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>68654355</v>
+        <v>68654361</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,39 +2704,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540534.8773027005</v>
+        <v>540691</v>
       </c>
       <c r="R21" t="n">
-        <v>7233072.036205481</v>
+        <v>7233113</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2903,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,37 +2800,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>68654348</v>
+        <v>68654409</v>
       </c>
       <c r="B22" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>1506</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2980,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540593.8839912249</v>
+        <v>540537</v>
       </c>
       <c r="R22" t="n">
-        <v>7232936.859621153</v>
+        <v>7232628</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3015,7 +2870,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +2880,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,53 +2907,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>68654405</v>
+        <v>67530747</v>
       </c>
       <c r="B23" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>1841</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Krutskogen, Ås lm</t>
+          <t>Antonskullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540372.8284589234</v>
+        <v>540146</v>
       </c>
       <c r="R23" t="n">
-        <v>7232846.103948628</v>
+        <v>7232435</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3122,22 +2972,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>08:03</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>08:03</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,27 +2992,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>68654340</v>
+        <v>68654336</v>
       </c>
       <c r="B24" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3180,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3204,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540438.8263854914</v>
+        <v>540798</v>
       </c>
       <c r="R24" t="n">
-        <v>7232783.206788406</v>
+        <v>7232873</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3239,7 +3074,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3084,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,37 +3111,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>68654339</v>
+        <v>68654342</v>
       </c>
       <c r="B25" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3316,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540734.201943661</v>
+        <v>540424</v>
       </c>
       <c r="R25" t="n">
-        <v>7232848.130912361</v>
+        <v>7232844</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3351,7 +3181,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3191,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,15 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>68654334</v>
+        <v>68654347</v>
       </c>
       <c r="B26" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3404,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3428,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540910.9518903529</v>
+        <v>540585</v>
       </c>
       <c r="R26" t="n">
-        <v>7232830.008260449</v>
+        <v>7232928</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3463,7 +3288,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3298,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,37 +3325,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>68654351</v>
+        <v>68654349</v>
       </c>
       <c r="B27" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3540,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540632.0633276261</v>
+        <v>540594</v>
       </c>
       <c r="R27" t="n">
-        <v>7232971.802191923</v>
+        <v>7232938</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3575,7 +3395,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3405,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,37 +3432,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>68654379</v>
+        <v>68654350</v>
       </c>
       <c r="B28" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3652,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540789.83695576</v>
+        <v>540631</v>
       </c>
       <c r="R28" t="n">
-        <v>7233049.107400874</v>
+        <v>7232975</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3687,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3724,37 +3539,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>68654335</v>
+        <v>68654369</v>
       </c>
       <c r="B29" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3764,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540838.1332003378</v>
+        <v>540989</v>
       </c>
       <c r="R29" t="n">
-        <v>7232868.87495881</v>
+        <v>7233212</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3799,7 +3609,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3619,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,37 +3646,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>68654393</v>
+        <v>68654394</v>
       </c>
       <c r="B30" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3876,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540168.1759055944</v>
+        <v>540169</v>
       </c>
       <c r="R30" t="n">
-        <v>7233093.044059844</v>
+        <v>7233093</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3911,7 +3716,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3726,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,15 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>68654378</v>
+        <v>67530722</v>
       </c>
       <c r="B31" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,37 +3764,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>2166</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Krutskogen, Ås lm</t>
+          <t>Antonskullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540798.0165780541</v>
+        <v>540136</v>
       </c>
       <c r="R31" t="n">
-        <v>7233034.950306408</v>
+        <v>7232367</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4018,22 +3818,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4048,65 +3838,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>68654344</v>
+        <v>67530642</v>
       </c>
       <c r="B32" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>2387</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Krutskogen, Ås lm</t>
+          <t>Antonskullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540438.8042636978</v>
+        <v>540145</v>
       </c>
       <c r="R32" t="n">
-        <v>7232846.167654229</v>
+        <v>7232349</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4130,22 +3915,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,27 +3935,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström, Nils Ericson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>68654371</v>
+        <v>67530704</v>
       </c>
       <c r="B33" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,37 +3958,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>2813</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Krutskogen, Ås lm</t>
+          <t>Antonskullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540981.1825073647</v>
+        <v>540127</v>
       </c>
       <c r="R33" t="n">
-        <v>7233128.983760099</v>
+        <v>7232410</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4242,22 +4012,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2017-09-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,27 +4032,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Isak Vahlström, Nils Ericson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>68654406</v>
+        <v>68654335</v>
       </c>
       <c r="B34" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,21 +4055,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4324,10 +4079,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540375.8097275326</v>
+        <v>540838</v>
       </c>
       <c r="R34" t="n">
-        <v>7232843.206572804</v>
+        <v>7232869</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4359,7 +4114,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4369,7 +4124,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4396,37 +4151,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>68654391</v>
+        <v>68654338</v>
       </c>
       <c r="B35" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>918</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4436,10 +4186,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540329.9949363009</v>
+        <v>540799</v>
       </c>
       <c r="R35" t="n">
-        <v>7233059.156425997</v>
+        <v>7232872</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4471,7 +4221,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4481,7 +4231,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,37 +4258,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>68654377</v>
+        <v>68654362</v>
       </c>
       <c r="B36" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4548,10 +4293,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540816.0217645835</v>
+        <v>540970</v>
       </c>
       <c r="R36" t="n">
-        <v>7233009.17702923</v>
+        <v>7232977</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4583,7 +4328,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,7 +4338,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4620,15 +4365,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>68654362</v>
+        <v>68654370</v>
       </c>
       <c r="B37" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,10 +4400,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540969.8475029584</v>
+        <v>540991</v>
       </c>
       <c r="R37" t="n">
-        <v>7232976.891488444</v>
+        <v>7233215</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4695,7 +4435,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4705,7 +4445,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4732,15 +4472,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>68654346</v>
+        <v>68654373</v>
       </c>
       <c r="B38" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4748,21 +4483,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4772,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540583.9506093966</v>
+        <v>541012</v>
       </c>
       <c r="R38" t="n">
-        <v>7232925.810160669</v>
+        <v>7233012</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4807,7 +4542,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4817,7 +4552,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4844,37 +4579,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>68654341</v>
+        <v>68654374</v>
       </c>
       <c r="B39" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4884,10 +4614,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540437.9228136457</v>
+        <v>541038</v>
       </c>
       <c r="R39" t="n">
-        <v>7232787.811607144</v>
+        <v>7233008</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4919,7 +4649,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4929,7 +4659,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4956,15 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>68654338</v>
+        <v>68654375</v>
       </c>
       <c r="B40" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4996,10 +4721,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540799.0068710529</v>
+        <v>541032</v>
       </c>
       <c r="R40" t="n">
-        <v>7232872.111474168</v>
+        <v>7232997</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5031,7 +4756,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5041,7 +4766,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,37 +4793,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>68654349</v>
+        <v>68654379</v>
       </c>
       <c r="B41" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5108,10 +4828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540593.8666761188</v>
+        <v>540790</v>
       </c>
       <c r="R41" t="n">
-        <v>7232938.118556147</v>
+        <v>7233049</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5143,7 +4863,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +4873,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5180,55 +4900,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>68654356</v>
+        <v>68654343</v>
       </c>
       <c r="B42" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540584.1206241699</v>
+        <v>540427</v>
       </c>
       <c r="R42" t="n">
-        <v>7233157.911872639</v>
+        <v>7232842</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5260,7 +4970,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5270,7 +4980,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5297,37 +5007,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>68654342</v>
+        <v>68654348</v>
       </c>
       <c r="B43" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5337,10 +5042,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540424.1275800862</v>
+        <v>540594</v>
       </c>
       <c r="R43" t="n">
-        <v>7232843.867925717</v>
+        <v>7232937</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5372,7 +5077,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5382,7 +5087,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5409,55 +5114,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>68654332</v>
+        <v>68654351</v>
       </c>
       <c r="B44" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540942.0822045237</v>
+        <v>540632</v>
       </c>
       <c r="R44" t="n">
-        <v>7232767.058328449</v>
+        <v>7232972</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5489,7 +5184,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5499,7 +5194,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5526,37 +5221,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>68654333</v>
+        <v>68654371</v>
       </c>
       <c r="B45" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5566,10 +5256,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540916.8224584482</v>
+        <v>540981</v>
       </c>
       <c r="R45" t="n">
-        <v>7232830.929117716</v>
+        <v>7233129</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5601,7 +5291,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5611,7 +5301,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5638,37 +5328,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>68654409</v>
+        <v>68654372</v>
       </c>
       <c r="B46" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5678,10 +5363,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540537.1936342487</v>
+        <v>540990</v>
       </c>
       <c r="R46" t="n">
-        <v>7232627.986763064</v>
+        <v>7233120</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5713,7 +5398,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5723,7 +5408,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5750,15 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>68654337</v>
+        <v>68654378</v>
       </c>
       <c r="B47" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5766,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5790,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540796.8945132684</v>
+        <v>540798</v>
       </c>
       <c r="R47" t="n">
-        <v>7232872.921744964</v>
+        <v>7233035</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5825,7 +5505,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5835,7 +5515,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5862,37 +5542,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>68654385</v>
+        <v>68654380</v>
       </c>
       <c r="B48" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5902,10 +5577,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540309.1217300164</v>
+        <v>540760</v>
       </c>
       <c r="R48" t="n">
-        <v>7233172.18970097</v>
+        <v>7233080</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5937,7 +5612,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5947,7 +5622,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5974,15 +5649,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>68654373</v>
+        <v>68654393</v>
       </c>
       <c r="B49" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5990,21 +5660,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6014,10 +5684,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541011.8031286283</v>
+        <v>540168</v>
       </c>
       <c r="R49" t="n">
-        <v>7233011.891071759</v>
+        <v>7233093</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6049,7 +5719,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6059,7 +5729,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6086,55 +5756,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>68654331</v>
+        <v>68654337</v>
       </c>
       <c r="B50" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540945.9510268972</v>
+        <v>540797</v>
       </c>
       <c r="R50" t="n">
-        <v>7232760.815736799</v>
+        <v>7232873</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6166,7 +5826,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6176,7 +5836,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6203,37 +5863,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>68654336</v>
+        <v>68654346</v>
       </c>
       <c r="B51" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6243,10 +5898,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540798.154966933</v>
+        <v>540584</v>
       </c>
       <c r="R51" t="n">
-        <v>7232872.939167464</v>
+        <v>7232926</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6278,7 +5933,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6288,7 +5943,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6315,50 +5970,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>68654361</v>
+        <v>68654331</v>
       </c>
       <c r="B52" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540691.0507730527</v>
+        <v>540946</v>
       </c>
       <c r="R52" t="n">
-        <v>7233112.797956252</v>
+        <v>7232761</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6390,7 +6045,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6400,7 +6055,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6427,15 +6082,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>68654408</v>
+        <v>68654332</v>
       </c>
       <c r="B53" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6443,34 +6093,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540336.131312574</v>
+        <v>540942</v>
       </c>
       <c r="R53" t="n">
-        <v>7232733.110753685</v>
+        <v>7232767</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6502,7 +6157,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6512,7 +6167,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6539,15 +6194,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>114009437</v>
+        <v>68654345</v>
       </c>
       <c r="B54" t="n">
-        <v>57185</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6555,44 +6205,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102110</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kittelfjäll, Ås lm</t>
+          <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540840</v>
+        <v>540590</v>
       </c>
       <c r="R54" t="n">
-        <v>7232806</v>
+        <v>7232919</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6616,27 +6264,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2017-09-09</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2017-09-09</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>En individ följdes i tubkikaren över skogen utmed Dikasjön innan den tappades bakom trädgrupp, sannolikt fjällvråk även om viss osäkerhet fanns pga mjölkvit bakgrund. Vitt på stjärten hade den.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6651,19 +6294,1136 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>68654354</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>540556</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7233066</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>68654355</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>540535</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7233072</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>68654356</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>540584</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7233158</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>68654358</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>540602</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7233254</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>68654389</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>540268</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7233063</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>68654392</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>540411</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7233077</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>68654395</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>540143</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7233007</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>114009437</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>540840</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7232806</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>En individ följdes i tubkikaren över skogen utmed Dikasjön innan den tappades bakom trädgrupp, sannolikt fjällvråk även om viss osäkerhet fanns pga mjölkvit bakgrund. Vitt på stjärten hade den.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
           <t>Samuel Holdar</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
+      <c r="AX62" t="inlineStr">
         <is>
           <t>Anders Tranberg</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr">
+      <c r="AY62" t="inlineStr">
         <is>
           <t>EEN0069 Dikanäs-Kittelfjäll</t>
         </is>
       </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>68654405</v>
+      </c>
+      <c r="B63" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>540373</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7232846</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>68654406</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>540376</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7232843</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2017-09-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
